--- a/artfynd/A 4212-2023 artfynd.xlsx
+++ b/artfynd/A 4212-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4212-2023 artfynd.xlsx
+++ b/artfynd/A 4212-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,6 +1056,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106015371</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57245</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergstorp , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580717</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571252</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4212-2023 artfynd.xlsx
+++ b/artfynd/A 4212-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105911181</v>
+        <v>106015371</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergstorp, Srm</t>
+          <t>Bergstorp , Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580673.0450254382</v>
+        <v>580717</v>
       </c>
       <c r="R2" t="n">
-        <v>6571284.471602775</v>
+        <v>6571252</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor mängd blåsippa i skogsglänta</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,12 +797,7 @@
         <v>106015656</v>
       </c>
       <c r="B3" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580694.4797328119</v>
+        <v>580694</v>
       </c>
       <c r="R3" t="n">
-        <v>6571263.964749543</v>
+        <v>6571264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -934,51 +915,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106015371</v>
+        <v>106538494</v>
       </c>
       <c r="B4" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580717</v>
+        <v>580735</v>
       </c>
       <c r="R4" t="n">
-        <v>6571252</v>
+        <v>6571227</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,22 +992,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett tiotal plantor inom ett område av 4 kvm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,6 +1036,254 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105911181</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580673</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571284</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor mängd blåsippa i skogsglänta</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>105911293</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580686</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571243</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Utspridda plantor i glänta</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4212-2023 artfynd.xlsx
+++ b/artfynd/A 4212-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106015371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106015656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106538494</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911181</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1284,8 +1309,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>